--- a/data/trans_orig/IP28-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP28-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5689</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15185</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,49 +748,49 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>15,37%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>8975</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5335</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>14564</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>9,26%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>5,51%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
           <t>15,03%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8975</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4691</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>14355</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>9,26%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>14,82%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>28</t>
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13204</t>
+          <t>13001</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26437</t>
+          <t>26467</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80142</t>
+          <t>80228</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91875</t>
+          <t>92231</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68982</t>
+          <t>68964</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82306</t>
+          <t>82050</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>153714</t>
+          <t>152567</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>170584</t>
+          <t>170440</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,11%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8398</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6462</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16397</t>
+          <t>16726</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8728</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21211</t>
+          <t>20851</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4144</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>639</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>6397</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8320</t>
+          <t>8725</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10474</t>
+          <t>10439</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15580</t>
+          <t>15069</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69887</t>
+          <t>69831</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79473</t>
+          <t>79355</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70834</t>
+          <t>70697</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80030</t>
+          <t>80057</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>143645</t>
+          <t>144549</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157453</t>
+          <t>157383</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9769</t>
+          <t>9744</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>641</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12453</t>
+          <t>11788</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5895</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>674</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6603</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6188</t>
+          <t>5561</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15982</t>
+          <t>15186</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19057</t>
+          <t>19220</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54511</t>
+          <t>54673</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>63096</t>
+          <t>62917</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>67914</t>
+          <t>68491</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>81799</t>
+          <t>81374</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>127323</t>
+          <t>126349</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>142532</t>
+          <t>142518</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,19%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>1683</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,47 +2112,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>11,98%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>10670</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>6281</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>16190</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>10,89%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>10670</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>6160</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>16724</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>10,89%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9353</t>
+          <t>8963</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21410</t>
+          <t>20354</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4794</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>5381</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7015</t>
+          <t>8058</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11528</t>
+          <t>11072</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6638</t>
+          <t>6921</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17239</t>
+          <t>17421</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11375</t>
+          <t>11454</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24580</t>
+          <t>24560</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>163079</t>
+          <t>162610</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>178638</t>
+          <t>178123</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>155518</t>
+          <t>155006</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>172355</t>
+          <t>172264</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>323214</t>
+          <t>324102</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>346615</t>
+          <t>346168</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,08%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>13307</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26254</t>
+          <t>26341</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14665</t>
+          <t>15077</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28779</t>
+          <t>28741</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>31021</t>
+          <t>30998</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>49753</t>
+          <t>50703</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>595</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>725</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>7056</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9956</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7238</t>
+          <t>6641</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>17199</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13464</t>
+          <t>14384</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13835</t>
+          <t>13088</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27998</t>
+          <t>27423</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>70827</t>
+          <t>70308</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>84845</t>
+          <t>84904</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>102173</t>
+          <t>101757</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>114758</t>
+          <t>114485</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>177894</t>
+          <t>177755</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>197167</t>
+          <t>195800</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,26%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6014</t>
+          <t>6392</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15907</t>
+          <t>17402</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>4653</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13573</t>
+          <t>14348</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12349</t>
+          <t>13004</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>26351</t>
+          <t>26380</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>670</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6992</t>
+          <t>6873</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>7678</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2613</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10099</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11160</t>
+          <t>11092</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>7814</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>17869</t>
+          <t>18464</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>51880</t>
+          <t>52170</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>63456</t>
+          <t>63552</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>56720</t>
+          <t>56957</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>65978</t>
+          <t>65907</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>112024</t>
+          <t>111601</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>126672</t>
+          <t>126879</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,89%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>5984</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>15500</t>
+          <t>15090</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>681</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6243</t>
+          <t>6659</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>7684</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>18620</t>
+          <t>18727</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>4594</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>31024</t>
+          <t>30648</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>50304</t>
+          <t>49896</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>39791</t>
+          <t>40472</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>63158</t>
+          <t>61933</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4197,47 +4197,47 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>9,14%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>90052</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>76732</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>105766</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>6,89%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
           <t>5,87%</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>90052</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>76322</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>105557</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>6,89%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>513722</t>
+          <t>513768</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>541988</t>
+          <t>542387</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4295,12 +4295,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>547402</t>
+          <t>547462</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>578529</t>
+          <t>577454</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1068959</t>
+          <t>1069956</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1111827</t>
+          <t>1112512</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,12 +4345,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,15%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>42331</t>
+          <t>40604</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>63644</t>
+          <t>63580</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>44747</t>
+          <t>44814</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>67455</t>
+          <t>67104</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>91168</t>
+          <t>92257</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>123933</t>
+          <t>122376</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>13757</t>
+          <t>14608</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>4621</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13894</t>
+          <t>13408</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>10701</t>
+          <t>10995</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>24862</t>
+          <t>24730</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -4950,12 +4950,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8824</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4965,12 +4965,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>7187</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4545</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13962</t>
+          <t>13100</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5035,12 +5035,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -5063,12 +5063,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67382</t>
+          <t>66277</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76893</t>
+          <t>76809</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68463</t>
+          <t>67774</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77977</t>
+          <t>78021</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5113,12 +5113,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>138385</t>
+          <t>139309</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>152581</t>
+          <t>152570</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,03%</t>
         </is>
       </c>
     </row>
@@ -5176,12 +5176,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>1473</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5191,12 +5191,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11320</t>
+          <t>10431</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5951</t>
+          <t>5811</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15987</t>
+          <t>15728</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5261,12 +5261,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>4681</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>741</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5374,12 +5374,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10172</t>
+          <t>9944</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10717</t>
+          <t>11185</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7128</t>
+          <t>7065</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17287</t>
+          <t>17871</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5604,12 +5604,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -5632,12 +5632,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63541</t>
+          <t>63035</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75759</t>
+          <t>75638</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5647,12 +5647,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67661</t>
+          <t>66615</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78266</t>
+          <t>78229</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>135435</t>
+          <t>135753</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>150856</t>
+          <t>151238</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5717,12 +5717,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,43%</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5745,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>5050</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15554</t>
+          <t>15470</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10816</t>
+          <t>11403</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10374</t>
+          <t>10395</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22349</t>
+          <t>23025</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3898</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>629</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -6088,12 +6088,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10870</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3488</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11832</t>
+          <t>11177</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19063</t>
+          <t>18350</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -6201,12 +6201,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54241</t>
+          <t>54586</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>65191</t>
+          <t>65402</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>51739</t>
+          <t>52657</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>64661</t>
+          <t>64535</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>110780</t>
+          <t>110246</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>126902</t>
+          <t>126345</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>82,61%</t>
         </is>
       </c>
     </row>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13448</t>
+          <t>12970</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5426</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15331</t>
+          <t>14966</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12433</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26286</t>
+          <t>25457</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>621</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5370</t>
+          <t>5572</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>747</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>6903</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -6657,12 +6657,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15278</t>
+          <t>15941</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6556</t>
+          <t>6618</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17124</t>
+          <t>18207</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14043</t>
+          <t>14178</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28867</t>
+          <t>29054</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6770,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>142652</t>
+          <t>142911</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>160194</t>
+          <t>160197</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6785,7 +6785,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>165358</t>
+          <t>165354</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>183207</t>
+          <t>182948</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>313389</t>
+          <t>314567</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>338917</t>
+          <t>338067</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,79%</t>
         </is>
       </c>
     </row>
@@ -6883,12 +6883,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15381</t>
+          <t>15120</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29813</t>
+          <t>29410</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9875</t>
+          <t>10023</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23590</t>
+          <t>23177</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>28881</t>
+          <t>29106</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>48714</t>
+          <t>49218</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -6996,12 +6996,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8836</t>
+          <t>8560</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1774</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8676</t>
+          <t>8615</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14197</t>
+          <t>13718</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6445</t>
+          <t>6764</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16983</t>
+          <t>17762</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>10050</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22195</t>
+          <t>22099</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>18994</t>
+          <t>18746</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>35398</t>
+          <t>34222</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -7339,12 +7339,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>92123</t>
+          <t>91073</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>108239</t>
+          <t>108514</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>94264</t>
+          <t>93169</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>110139</t>
+          <t>109888</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>189320</t>
+          <t>191530</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>213634</t>
+          <t>214856</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,96%</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13560</t>
+          <t>13075</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27752</t>
+          <t>26594</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18088</t>
+          <t>19104</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>22430</t>
+          <t>22552</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41380</t>
+          <t>40723</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -7565,12 +7565,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>8008</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>11105</t>
+          <t>11189</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>4684</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>13557</t>
+          <t>13911</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>19625</t>
+          <t>18793</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,34%</t>
         </is>
       </c>
     </row>
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>32056</t>
+          <t>32082</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>42498</t>
+          <t>42215</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>48730</t>
+          <t>48786</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>60500</t>
+          <t>60438</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>83745</t>
+          <t>85065</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>99261</t>
+          <t>99771</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>81,43%</t>
         </is>
       </c>
     </row>
@@ -8021,12 +8021,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3644</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12869</t>
+          <t>12490</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4661</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>13569</t>
+          <t>13494</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10128</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>22653</t>
+          <t>21906</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4441</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>31901</t>
+          <t>32709</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>52936</t>
+          <t>52911</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>38782</t>
+          <t>40295</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>62460</t>
+          <t>63232</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>76117</t>
+          <t>77861</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>106531</t>
+          <t>107667</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>475644</t>
+          <t>474914</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>508423</t>
+          <t>507657</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>522220</t>
+          <t>522160</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>554039</t>
+          <t>555586</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1009440</t>
+          <t>1007444</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1054192</t>
+          <t>1052550</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,52%</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>58350</t>
+          <t>57989</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>85914</t>
+          <t>84815</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>46387</t>
+          <t>46890</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>70593</t>
+          <t>70486</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8640,12 +8640,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>110947</t>
+          <t>111266</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>147537</t>
+          <t>145473</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -8703,12 +8703,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>19190</t>
+          <t>18434</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6973</t>
+          <t>6799</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>18274</t>
+          <t>17578</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>16161</t>
+          <t>16804</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>31725</t>
+          <t>32305</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -9167,12 +9167,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>547</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9182,12 +9182,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9217,12 +9217,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11160</t>
+          <t>11114</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9252,12 +9252,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -9280,12 +9280,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66257</t>
+          <t>66260</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73692</t>
+          <t>73830</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74538</t>
+          <t>75051</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84346</t>
+          <t>84478</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9330,12 +9330,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>144582</t>
+          <t>144722</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>156296</t>
+          <t>156422</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9365,12 +9365,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7364</t>
+          <t>7035</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9408,12 +9408,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2750</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10877</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5065</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14769</t>
+          <t>14672</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -9736,12 +9736,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7182</t>
+          <t>7164</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9751,12 +9751,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9771,12 +9771,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10640</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9806,12 +9806,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4605</t>
+          <t>4553</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14559</t>
+          <t>14016</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9821,12 +9821,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -9849,12 +9849,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80155</t>
+          <t>79565</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>89356</t>
+          <t>89215</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85975</t>
+          <t>86031</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>95770</t>
+          <t>95435</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>168931</t>
+          <t>168849</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>183265</t>
+          <t>182606</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -9962,12 +9962,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10298</t>
+          <t>10990</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1538</t>
+          <t>1528</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5729</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15903</t>
+          <t>16302</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -10305,12 +10305,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2460</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9781</t>
+          <t>10089</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14361</t>
+          <t>13912</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -10418,12 +10418,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45991</t>
+          <t>45691</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54300</t>
+          <t>54186</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10433,12 +10433,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>51971</t>
+          <t>52047</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62560</t>
+          <t>62187</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>100656</t>
+          <t>101521</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>114297</t>
+          <t>113870</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>88,9%</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8979</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1423</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>8079</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4786</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14117</t>
+          <t>14093</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -10679,12 +10679,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6430</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10694,12 +10694,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>681</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>6355</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10729,12 +10729,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -10874,12 +10874,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13153</t>
+          <t>12936</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9736</t>
+          <t>9869</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22271</t>
+          <t>22634</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>15806</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30784</t>
+          <t>32163</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10959,12 +10959,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -10987,12 +10987,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>164729</t>
+          <t>165116</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>181458</t>
+          <t>181116</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>145174</t>
+          <t>145057</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>162586</t>
+          <t>163268</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>316621</t>
+          <t>315781</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>341066</t>
+          <t>339739</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11072,12 +11072,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,15%</t>
         </is>
       </c>
     </row>
@@ -11100,12 +11100,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12052</t>
+          <t>12001</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24718</t>
+          <t>25243</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11135,12 +11135,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23888</t>
+          <t>24510</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11150,12 +11150,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>25603</t>
+          <t>25398</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>44656</t>
+          <t>44266</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11185,12 +11185,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -11213,12 +11213,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7077</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9052</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11298,12 +11298,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -11443,12 +11443,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8667</t>
+          <t>8826</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1434</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>8198</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4584</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13623</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11528,12 +11528,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -11556,12 +11556,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>95988</t>
+          <t>96747</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>107446</t>
+          <t>108231</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11591,12 +11591,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>106657</t>
+          <t>106941</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>118210</t>
+          <t>118489</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11626,12 +11626,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>206689</t>
+          <t>206537</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>223479</t>
+          <t>223266</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,36%</t>
         </is>
       </c>
     </row>
@@ -11669,12 +11669,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14366</t>
+          <t>13592</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11704,12 +11704,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4152</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13571</t>
+          <t>13455</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11739,12 +11739,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10913</t>
+          <t>11170</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>24186</t>
+          <t>24379</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11754,12 +11754,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -11787,7 +11787,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11802,7 +11802,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11817,12 +11817,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>614</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -11852,12 +11852,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7660</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11867,12 +11867,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -12012,12 +12012,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1427</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>7979</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12027,12 +12027,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9108</t>
+          <t>10164</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12067,7 +12067,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12082,12 +12082,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>14918</t>
+          <t>14890</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12097,12 +12097,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -12125,12 +12125,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>41809</t>
+          <t>42116</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>51248</t>
+          <t>50840</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12160,12 +12160,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>48535</t>
+          <t>48171</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>57734</t>
+          <t>57639</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12195,12 +12195,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>93210</t>
+          <t>93137</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>106855</t>
+          <t>106493</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12210,12 +12210,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,28%</t>
         </is>
       </c>
     </row>
@@ -12238,12 +12238,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8804</t>
+          <t>8826</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12273,12 +12273,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9057</t>
+          <t>9020</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12308,12 +12308,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>14675</t>
+          <t>14678</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12323,7 +12323,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -12356,7 +12356,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>2531</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -12581,12 +12581,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16941</t>
+          <t>17773</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>32293</t>
+          <t>32989</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12616,12 +12616,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>29981</t>
+          <t>28532</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>49511</t>
+          <t>47759</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12651,12 +12651,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>50700</t>
+          <t>51947</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>75328</t>
+          <t>76601</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12666,12 +12666,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -12694,12 +12694,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>518274</t>
+          <t>517309</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>544700</t>
+          <t>543632</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12729,12 +12729,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>536574</t>
+          <t>536741</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>564986</t>
+          <t>564820</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12764,12 +12764,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1062567</t>
+          <t>1061671</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1101681</t>
+          <t>1099516</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12779,12 +12779,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,36%</t>
         </is>
       </c>
     </row>
@@ -12807,12 +12807,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>34784</t>
+          <t>35174</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>55388</t>
+          <t>55961</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12842,12 +12842,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>32779</t>
+          <t>33040</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>53645</t>
+          <t>53620</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -12877,12 +12877,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>73766</t>
+          <t>72649</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>103444</t>
+          <t>103978</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12892,12 +12892,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -12920,12 +12920,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>10299</t>
+          <t>10737</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12955,12 +12955,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>2671</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10986</t>
+          <t>10686</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12990,12 +12990,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>7143</t>
+          <t>7369</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>17953</t>
+          <t>17987</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13005,12 +13005,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -13384,12 +13384,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>5649</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15581</t>
+          <t>15170</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13399,12 +13399,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>7736</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32038</t>
+          <t>34909</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13434,12 +13434,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16081</t>
+          <t>15848</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44337</t>
+          <t>45096</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13469,12 +13469,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -13497,12 +13497,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81945</t>
+          <t>82078</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93586</t>
+          <t>93756</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13512,12 +13512,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>97187</t>
+          <t>95326</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>123060</t>
+          <t>122729</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13547,12 +13547,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>185281</t>
+          <t>184013</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>213494</t>
+          <t>212920</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13582,12 +13582,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,65%</t>
         </is>
       </c>
     </row>
@@ -13610,12 +13610,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8318</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13625,12 +13625,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13645,12 +13645,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>2318</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10885</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13660,12 +13660,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13680,12 +13680,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5553</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15828</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13695,12 +13695,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13743,7 +13743,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13763,7 +13763,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>5074</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13778,7 +13778,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13793,12 +13793,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>703</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>7145</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13813,7 +13813,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -13953,12 +13953,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8950</t>
+          <t>8804</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19433</t>
+          <t>20522</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -13968,12 +13968,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>7133</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18781</t>
+          <t>18372</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14003,12 +14003,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18012</t>
+          <t>17639</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>34331</t>
+          <t>34144</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14038,12 +14038,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -14066,12 +14066,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65727</t>
+          <t>64808</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79032</t>
+          <t>78992</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14081,12 +14081,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14101,12 +14101,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68946</t>
+          <t>68598</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82471</t>
+          <t>82141</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14116,12 +14116,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14136,12 +14136,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>139237</t>
+          <t>138605</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159093</t>
+          <t>158324</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14151,12 +14151,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,57%</t>
         </is>
       </c>
     </row>
@@ -14179,12 +14179,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12219</t>
+          <t>12527</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14194,12 +14194,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14214,12 +14214,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>2498</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10551</t>
+          <t>10797</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14229,12 +14229,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14249,12 +14249,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>8076</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20415</t>
+          <t>20014</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14264,12 +14264,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -14297,7 +14297,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5313</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14332,7 +14332,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3148</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14347,7 +14347,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14362,12 +14362,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>589</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14382,7 +14382,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -14522,12 +14522,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>397</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14557,12 +14557,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8710</t>
+          <t>8173</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14572,12 +14572,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14592,12 +14592,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11975</t>
+          <t>11064</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14607,12 +14607,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -14635,12 +14635,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41890</t>
+          <t>41900</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49081</t>
+          <t>48821</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -14650,12 +14650,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -14670,12 +14670,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50860</t>
+          <t>51481</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59979</t>
+          <t>60215</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -14705,12 +14705,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>96075</t>
+          <t>95861</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>107777</t>
+          <t>107535</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -14720,12 +14720,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -14748,12 +14748,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>798</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6638</t>
+          <t>6570</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14763,12 +14763,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14783,12 +14783,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14798,12 +14798,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14818,12 +14818,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2716</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10802</t>
+          <t>10937</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14936,7 +14936,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>833</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10633</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26290</t>
+          <t>26058</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15106,12 +15106,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15126,12 +15126,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8896</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24436</t>
+          <t>25213</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15141,12 +15141,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15161,12 +15161,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22495</t>
+          <t>23060</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44599</t>
+          <t>44463</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15176,12 +15176,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -15204,12 +15204,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>169572</t>
+          <t>168960</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>194718</t>
+          <t>192580</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15219,12 +15219,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15239,12 +15239,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>153845</t>
+          <t>154631</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>181267</t>
+          <t>181806</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15254,12 +15254,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15274,12 +15274,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>334645</t>
+          <t>331373</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>369122</t>
+          <t>369127</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -15317,12 +15317,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>9705</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25232</t>
+          <t>25052</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15332,12 +15332,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15352,12 +15352,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20284</t>
+          <t>19334</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>43796</t>
+          <t>42430</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15367,12 +15367,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15387,12 +15387,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>32952</t>
+          <t>32521</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>60800</t>
+          <t>62378</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15402,12 +15402,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -15430,12 +15430,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>505</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>6342</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15445,12 +15445,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15485,7 +15485,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15500,12 +15500,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1369</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>8795</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15515,12 +15515,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -15660,12 +15660,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23503</t>
+          <t>22335</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15675,12 +15675,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15695,12 +15695,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>7602</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19790</t>
+          <t>20848</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15710,12 +15710,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15730,12 +15730,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15321</t>
+          <t>15448</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>34850</t>
+          <t>34945</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15745,12 +15745,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -15773,12 +15773,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>84311</t>
+          <t>83761</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>102585</t>
+          <t>102295</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15788,12 +15788,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15808,12 +15808,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>126453</t>
+          <t>125612</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>145852</t>
+          <t>145681</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15823,12 +15823,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15843,12 +15843,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>219011</t>
+          <t>216909</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>245496</t>
+          <t>244751</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15858,12 +15858,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,78%</t>
         </is>
       </c>
     </row>
@@ -15886,12 +15886,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17121</t>
+          <t>17263</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -15901,12 +15901,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -15921,12 +15921,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5433</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22037</t>
+          <t>20811</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -15936,12 +15936,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -15956,12 +15956,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>13125</t>
+          <t>14551</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32196</t>
+          <t>33225</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -15971,12 +15971,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>824</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9037</t>
+          <t>9354</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -16014,82 +16014,82 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>7,83%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>1537</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>4880</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>5181</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>1966</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>10506</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>7,57%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>1537</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>4998</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>5181</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>2166</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>10546</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -16229,12 +16229,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6258</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16244,12 +16244,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16264,12 +16264,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14248</t>
+          <t>13663</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16279,12 +16279,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16299,12 +16299,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>17834</t>
+          <t>17862</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16314,12 +16314,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -16342,12 +16342,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>57057</t>
+          <t>57290</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>65583</t>
+          <t>65529</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16357,12 +16357,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16377,12 +16377,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>51462</t>
+          <t>51247</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>63246</t>
+          <t>63454</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16392,12 +16392,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16412,12 +16412,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>112416</t>
+          <t>112298</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>126719</t>
+          <t>126938</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16427,12 +16427,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,09%</t>
         </is>
       </c>
     </row>
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>832</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6430</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16470,12 +16470,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16490,12 +16490,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>735</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>7458</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16505,12 +16505,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16525,12 +16525,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2586</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11170</t>
+          <t>11033</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16540,12 +16540,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -16573,7 +16573,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6268</t>
+          <t>6034</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16588,7 +16588,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16603,12 +16603,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>503</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>7188</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16618,12 +16618,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16638,12 +16638,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8931</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16653,12 +16653,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -16798,12 +16798,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>43742</t>
+          <t>44463</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>71796</t>
+          <t>71892</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16813,12 +16813,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16833,12 +16833,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>52692</t>
+          <t>51492</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>88160</t>
+          <t>86748</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16848,12 +16848,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16868,12 +16868,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>103827</t>
+          <t>104475</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>148237</t>
+          <t>147663</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16883,12 +16883,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>526206</t>
+          <t>526542</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>565594</t>
+          <t>564598</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -16926,12 +16926,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -16946,12 +16946,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>588099</t>
+          <t>588260</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>632483</t>
+          <t>634811</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -16961,12 +16961,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -16981,12 +16981,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1128900</t>
+          <t>1127248</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1186487</t>
+          <t>1185862</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -16996,12 +16996,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,68%</t>
         </is>
       </c>
     </row>
@@ -17024,12 +17024,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>33095</t>
+          <t>31844</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>56157</t>
+          <t>55506</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17039,12 +17039,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17059,12 +17059,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>44848</t>
+          <t>43679</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>75478</t>
+          <t>75327</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17074,12 +17074,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17094,12 +17094,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>83515</t>
+          <t>83643</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>123083</t>
+          <t>123729</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17109,12 +17109,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -17137,12 +17137,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4972</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>17025</t>
+          <t>16608</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17157,7 +17157,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17172,12 +17172,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3536</t>
+          <t>3921</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13116</t>
+          <t>14266</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17187,12 +17187,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17207,12 +17207,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>11000</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>25422</t>
+          <t>26932</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17222,12 +17222,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
